--- a/reports/一级子公司B_利润表_2026-12.xlsx
+++ b/reports/一级子公司B_利润表_2026-12.xlsx
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="F3" s="13" t="n">
-        <v>48006488</v>
+        <v>63507887</v>
       </c>
       <c r="G3" s="13" t="n"/>
       <c r="I3" s="5" t="n"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="F4" s="14" t="n">
-        <v>0</v>
+        <v>14231176</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>0</v>
+        <v>177065399</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="F5" s="14" t="n">
-        <v>0</v>
+        <v>198622</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>0</v>
+        <v>2492585</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>0</v>
+        <v>178839</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>0</v>
+        <v>2242397</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>0</v>
+        <v>149245</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>0</v>
+        <v>1868027</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2214,10 +2214,10 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>0</v>
+        <v>139596</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>0</v>
+        <v>1743133</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>0</v>
+        <v>79969</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>0</v>
+        <v>996040</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>0</v>
+        <v>60121</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>0</v>
+        <v>747133</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>48006488</v>
+        <v>62701495</v>
       </c>
       <c r="G11" s="13" t="n"/>
     </row>
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0</v>
+        <v>13424784</v>
       </c>
       <c r="G12" s="13" t="n"/>
     </row>
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>0</v>
+        <v>8039756</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>0</v>
+        <v>99728495</v>
       </c>
     </row>
     <row r="14" ht="20.25" customHeight="1">
@@ -2408,10 +2408,10 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>0</v>
+        <v>1204744</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>0</v>
+        <v>14964968</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>0</v>
+        <v>601250</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>0</v>
+        <v>7484504</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>0</v>
+        <v>3998752</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>0</v>
+        <v>49902316</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="F17" s="14" t="n">
-        <v>0</v>
+        <v>398876</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>0</v>
+        <v>4989907</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>0</v>
+        <v>298508</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>0</v>
+        <v>3741567</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>0</v>
+        <v>496791</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>0</v>
+        <v>6233722</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="F20" s="14" t="n">
-        <v>0</v>
+        <v>397243</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>0</v>
+        <v>4984888</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>47924563</v>
+        <v>47696973</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>587040139</v>
+        <v>586802396</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -2672,10 +2672,10 @@
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>81925</v>
+        <v>82080</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>988874</v>
+        <v>987906</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2705,10 +2705,10 @@
         </is>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0</v>
+        <v>897692</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>0</v>
+        <v>11205688</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0</v>
+        <v>599966</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>0</v>
+        <v>7470364</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>44324526</v>
+        <v>57263466</v>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>25169190</v>
+        <v>32358410</v>
       </c>
       <c r="G26" s="13" t="n"/>
     </row>
@@ -2833,10 +2833,10 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>150676</v>
+        <v>7236118</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>1869700</v>
+        <v>89722657</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>25018514</v>
+        <v>25122292</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>311488022</v>
+        <v>311668600</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2899,10 +2899,10 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0</v>
+        <v>1505622</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>0</v>
+        <v>18707023</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0</v>
+        <v>480857</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>0</v>
+        <v>5987753</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0</v>
+        <v>299805</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>0</v>
+        <v>3742680</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0</v>
+        <v>358874</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>0</v>
+        <v>4490818</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0</v>
+        <v>268592</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>0</v>
+        <v>3367270</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0</v>
+        <v>178823</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>0</v>
+        <v>2244020</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -3097,10 +3097,10 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0</v>
+        <v>148969</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>0</v>
+        <v>1869227</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -3130,10 +3130,10 @@
         </is>
       </c>
       <c r="F36" s="14" t="n">
-        <v>1192600</v>
+        <v>1192608</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>14953408</v>
+        <v>14947809</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="F37" s="14" t="n">
-        <v>39886</v>
+        <v>39819</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>498656</v>
+        <v>498106</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -3196,10 +3196,10 @@
         </is>
       </c>
       <c r="F38" s="14" t="n">
-        <v>2512544</v>
+        <v>2494404</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>31159192</v>
+        <v>31126534</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>14985749</v>
+        <v>15004141</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>196727621</v>
+        <v>196675866</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="F40" s="14" t="n">
-        <v>0</v>
+        <v>2506459</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>0</v>
+        <v>31132631</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="F41" s="14" t="n">
-        <v>464443</v>
+        <v>465902</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>5563919</v>
+        <v>5559122</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3328,10 +3328,10 @@
         </is>
       </c>
       <c r="F42" s="14" t="n">
-        <v>414152</v>
+        <v>414458</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>4943235</v>
+        <v>4943717</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="F43" s="14" t="n">
-        <v>30783</v>
+        <v>31076</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>370691</v>
+        <v>370954</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0</v>
+        <v>139666</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>0</v>
+        <v>1669953</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0</v>
+        <v>262889</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>0</v>
+        <v>3274625</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3460,10 +3460,10 @@
         </is>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0</v>
+        <v>92692</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>0</v>
+        <v>1113658</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0</v>
+        <v>69348</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>0</v>
+        <v>835135</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0</v>
+        <v>115348</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>0</v>
+        <v>1391462</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -3559,10 +3559,10 @@
         </is>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0</v>
+        <v>372508</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>0</v>
+        <v>4674784</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3592,10 +3592,10 @@
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0</v>
+        <v>61433</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>0</v>
+        <v>741442</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0</v>
+        <v>46114</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>0</v>
+        <v>555839</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -3658,10 +3658,10 @@
         </is>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0</v>
+        <v>76992</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>0</v>
+        <v>926099</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0</v>
+        <v>54020</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>0</v>
+        <v>648167</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0</v>
+        <v>38683</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>0</v>
+        <v>462997</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -3757,10 +3757,10 @@
         </is>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0</v>
+        <v>31016</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>0</v>
+        <v>370488</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0</v>
+        <v>23299</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>0</v>
+        <v>277972</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>3681962</v>
+        <v>6366663</v>
       </c>
       <c r="G57" s="13" t="n"/>
     </row>
@@ -3854,7 +3854,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>-108637</v>
+        <v>4487043</v>
       </c>
       <c r="G58" s="13" t="n"/>
     </row>
@@ -3885,10 +3885,10 @@
         </is>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0</v>
+        <v>150494</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>0</v>
+        <v>1870854</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3918,10 +3918,10 @@
         </is>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0</v>
+        <v>38705</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>0</v>
+        <v>464003</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3951,10 +3951,10 @@
         </is>
       </c>
       <c r="F61" s="14" t="n">
-        <v>61597</v>
+        <v>61774</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>741368</v>
+        <v>742436</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3984,7 +3984,7 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>3620365</v>
+        <v>6455383</v>
       </c>
       <c r="G62" s="13" t="n"/>
     </row>
@@ -4015,10 +4015,10 @@
         </is>
       </c>
       <c r="F63" s="14" t="n">
-        <v>1862830</v>
+        <v>1845178</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>22253276</v>
+        <v>22262263</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>1757535</v>
+        <v>4610205</v>
       </c>
       <c r="G64" s="13" t="n"/>
     </row>
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>1757535</v>
+        <v>4610205</v>
       </c>
       <c r="G66" s="13" t="n"/>
     </row>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>1757535</v>
+        <v>4610205</v>
       </c>
       <c r="G69" s="13" t="n"/>
     </row>
@@ -4410,7 +4410,7 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>1757535</v>
+        <v>4610205</v>
       </c>
       <c r="G76" s="13" t="n"/>
     </row>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>1757535</v>
+        <v>4610205</v>
       </c>
       <c r="G77" s="13" t="n"/>
     </row>
